--- a/Result/profitability/6165.xlsx
+++ b/Result/profitability/6165.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6687500000000001</v>
+        <v>0.7424999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>26.40875</v>
+        <v>26.935</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>0.53125</v>
+        <v>0.5775000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>25.51625</v>
+        <v>26.09875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="N4" t="n">
-        <v>24.04125</v>
+        <v>24.29375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2625</v>
+        <v>0.235</v>
       </c>
       <c r="N5" t="n">
-        <v>22.9275</v>
+        <v>23.03625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09625</v>
+        <v>0.08374999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>20.8075</v>
+        <v>20.89375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>19.03875</v>
+        <v>18.97375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.19</v>
+        <v>-0.22375</v>
       </c>
       <c r="N8" t="n">
-        <v>17.53375</v>
+        <v>17.57375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01250000000000005</v>
+        <v>-0.01250000000000003</v>
       </c>
       <c r="N10" t="n">
         <v>17.68</v>
@@ -1772,7 +1772,7 @@
         <v>-0.9</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01625000000000006</v>
+        <v>-0.01625000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>17.16125</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6165</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>876</v>
+      </c>
+      <c r="D75" t="n">
+        <v>611</v>
+      </c>
+      <c r="E75" t="n">
+        <v>265</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>103</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>83</v>
+      </c>
+      <c r="K75" t="n">
+        <v>61</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.82875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.69875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2477064220183487</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01069876295553329</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2200000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2115384615384616</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.870000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02963215258855589</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
